--- a/product_selector_out/STM32F429-439.xlsx
+++ b/product_selector_out/STM32F429-439.xlsx
@@ -20612,7 +20612,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -20722,7 +20722,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -20854,7 +20854,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -20986,7 +20986,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -21118,7 +21118,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -21250,7 +21250,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -21382,7 +21382,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -21514,7 +21514,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -21646,7 +21646,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -21778,7 +21778,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -21910,7 +21910,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -22042,7 +22042,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -22174,7 +22174,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -22306,7 +22306,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -22438,7 +22438,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -22548,7 +22548,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -22680,7 +22680,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -22812,7 +22812,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -22944,7 +22944,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -23076,7 +23076,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -23208,7 +23208,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -23340,7 +23340,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -23472,7 +23472,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -23582,7 +23582,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -23714,7 +23714,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -23846,7 +23846,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -23978,7 +23978,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -24110,7 +24110,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32F429-439.xlsx
+++ b/product_selector_out/STM32F429-439.xlsx
@@ -11506,14 +11506,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W13" s="8" t="inlineStr">
@@ -11536,9 +11536,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB13" s="8" t="inlineStr">
@@ -11843,14 +11843,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W14" s="8" t="inlineStr">
@@ -11873,9 +11873,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB14" s="8" t="inlineStr">
@@ -12180,14 +12180,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W15" s="8" t="inlineStr">
@@ -12210,9 +12210,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB15" s="8" t="inlineStr">
@@ -12547,9 +12547,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB16" s="8" t="inlineStr">
@@ -12854,14 +12854,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W17" s="8" t="inlineStr">
@@ -12884,9 +12884,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB17" s="8" t="inlineStr">
@@ -13221,9 +13221,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB18" s="8" t="inlineStr">
@@ -13528,14 +13528,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W19" s="8" t="inlineStr">
@@ -13558,9 +13558,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB19" s="8" t="inlineStr">
@@ -13865,14 +13865,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W20" s="8" t="inlineStr">
@@ -13895,9 +13895,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB20" s="8" t="inlineStr">
@@ -14232,9 +14232,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB21" s="8" t="inlineStr">
@@ -14539,14 +14539,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W22" s="8" t="inlineStr">
@@ -14569,9 +14569,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB22" s="8" t="inlineStr">
@@ -14876,14 +14876,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W23" s="8" t="inlineStr">
@@ -14906,9 +14906,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB23" s="8" t="inlineStr">
@@ -15213,14 +15213,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U24" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V24" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W24" s="8" t="inlineStr">
@@ -15243,9 +15243,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA24" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB24" s="8" t="inlineStr">
@@ -15580,9 +15580,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA25" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB25" s="8" t="inlineStr">
@@ -16224,14 +16224,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U27" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V27" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W27" s="8" t="inlineStr">
@@ -16254,9 +16254,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA27" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB27" s="8" t="inlineStr">
@@ -16591,9 +16591,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA28" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB28" s="8" t="inlineStr">
@@ -16898,14 +16898,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U29" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V29" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W29" s="8" t="inlineStr">
@@ -16928,9 +16928,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA29" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB29" s="8" t="inlineStr">
@@ -17265,9 +17265,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA30" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB30" s="8" t="inlineStr">
@@ -17572,14 +17572,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U31" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V31" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W31" s="8" t="inlineStr">
@@ -17602,9 +17602,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA31" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB31" s="8" t="inlineStr">
@@ -17939,9 +17939,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA32" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB32" s="8" t="inlineStr">
@@ -18246,14 +18246,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U33" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V33" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W33" s="8" t="inlineStr">
@@ -18276,9 +18276,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA33" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB33" s="8" t="inlineStr">
@@ -18920,14 +18920,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U35" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V35" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W35" s="8" t="inlineStr">
@@ -18950,9 +18950,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA35" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB35" s="8" t="inlineStr">
@@ -19257,14 +19257,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U36" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V36" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W36" s="8" t="inlineStr">
@@ -19287,9 +19287,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA36" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB36" s="8" t="inlineStr">
@@ -19624,9 +19624,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA37" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB37" s="8" t="inlineStr">
@@ -19961,9 +19961,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA38" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA38" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB38" s="8" t="inlineStr">

--- a/product_selector_out/STM32F429-439.xlsx
+++ b/product_selector_out/STM32F429-439.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO39"/>
+  <dimension ref="A1:BP39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.61328125" customWidth="1" min="1" max="1"/>
@@ -575,7 +575,8 @@
     <col width="21.765625" customWidth="1" min="64" max="64"/>
     <col width="18" customWidth="1" min="65" max="65"/>
     <col width="18" customWidth="1" min="66" max="66"/>
-    <col width="52" customWidth="1" min="67" max="67"/>
+    <col width="18" customWidth="1" min="67" max="67"/>
+    <col width="52" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -913,6 +914,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -1010,6 +1016,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1344,6 +1351,11 @@
       </c>
       <c r="BO12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f427ag.pdf</t>
         </is>
       </c>
@@ -1681,6 +1693,11 @@
       </c>
       <c r="BO13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f427ag.pdf</t>
         </is>
       </c>
@@ -2018,6 +2035,11 @@
       </c>
       <c r="BO14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f427ag.pdf</t>
         </is>
       </c>
@@ -2355,6 +2377,11 @@
       </c>
       <c r="BO15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f427ag.pdf</t>
         </is>
       </c>
@@ -2692,6 +2719,11 @@
       </c>
       <c r="BO16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f437ai.pdf</t>
         </is>
       </c>
@@ -3029,6 +3061,11 @@
       </c>
       <c r="BO17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f427ag.pdf</t>
         </is>
       </c>
@@ -3366,6 +3403,11 @@
       </c>
       <c r="BO18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f437ai.pdf</t>
         </is>
       </c>
@@ -3703,6 +3745,11 @@
       </c>
       <c r="BO19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f427ag.pdf</t>
         </is>
       </c>
@@ -4040,6 +4087,11 @@
       </c>
       <c r="BO20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f427ag.pdf</t>
         </is>
       </c>
@@ -4377,6 +4429,11 @@
       </c>
       <c r="BO21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f437ai.pdf</t>
         </is>
       </c>
@@ -4714,6 +4771,11 @@
       </c>
       <c r="BO22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f427ag.pdf</t>
         </is>
       </c>
@@ -5051,6 +5113,11 @@
       </c>
       <c r="BO23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f427ag.pdf</t>
         </is>
       </c>
@@ -5388,6 +5455,11 @@
       </c>
       <c r="BO24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f427ag.pdf</t>
         </is>
       </c>
@@ -5725,6 +5797,11 @@
       </c>
       <c r="BO25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f437ai.pdf</t>
         </is>
       </c>
@@ -6062,6 +6139,11 @@
       </c>
       <c r="BO26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f427ag.pdf</t>
         </is>
       </c>
@@ -6399,6 +6481,11 @@
       </c>
       <c r="BO27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f427ag.pdf</t>
         </is>
       </c>
@@ -6736,6 +6823,11 @@
       </c>
       <c r="BO28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f437ai.pdf</t>
         </is>
       </c>
@@ -7073,6 +7165,11 @@
       </c>
       <c r="BO29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f427ag.pdf</t>
         </is>
       </c>
@@ -7410,6 +7507,11 @@
       </c>
       <c r="BO30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f437ai.pdf</t>
         </is>
       </c>
@@ -7747,6 +7849,11 @@
       </c>
       <c r="BO31" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f427ag.pdf</t>
         </is>
       </c>
@@ -8084,6 +8191,11 @@
       </c>
       <c r="BO32" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f437ai.pdf</t>
         </is>
       </c>
@@ -8421,6 +8533,11 @@
       </c>
       <c r="BO33" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f427ag.pdf</t>
         </is>
       </c>
@@ -8758,6 +8875,11 @@
       </c>
       <c r="BO34" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f437ai.pdf</t>
         </is>
       </c>
@@ -9095,6 +9217,11 @@
       </c>
       <c r="BO35" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP35" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f427ag.pdf</t>
         </is>
       </c>
@@ -9432,6 +9559,11 @@
       </c>
       <c r="BO36" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP36" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f427ag.pdf</t>
         </is>
       </c>
@@ -9769,6 +9901,11 @@
       </c>
       <c r="BO37" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP37" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f437ai.pdf</t>
         </is>
       </c>
@@ -10106,6 +10243,11 @@
       </c>
       <c r="BO38" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP38" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f437ai.pdf</t>
         </is>
       </c>
@@ -10443,12 +10585,17 @@
       </c>
       <c r="BO39" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP39" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f437ai.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="67">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -10471,12 +10618,14 @@
     <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
     <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="A9:BP9"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="A1:BP8"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -10491,9 +10640,8 @@
     <mergeCell ref="BH10:BH11"/>
     <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="A9:BO9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="AL10:AL11"/>
@@ -10557,7 +10705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO39"/>
+  <dimension ref="A1:BP39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10627,6 +10775,7 @@
     <col width="16" customWidth="1" min="65" max="65"/>
     <col width="16" customWidth="1" min="66" max="66"/>
     <col width="16" customWidth="1" min="67" max="67"/>
+    <col width="16" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10970,6 +11119,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -11067,6 +11221,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -11399,7 +11554,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO12" s="6" t="inlineStr">
+      <c r="BO12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11736,7 +11896,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO13" s="6" t="inlineStr">
+      <c r="BO13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12073,7 +12238,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO14" s="6" t="inlineStr">
+      <c r="BO14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12410,7 +12580,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO15" s="6" t="inlineStr">
+      <c r="BO15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12747,7 +12922,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO16" s="6" t="inlineStr">
+      <c r="BO16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13084,7 +13264,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO17" s="6" t="inlineStr">
+      <c r="BO17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13421,7 +13606,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO18" s="6" t="inlineStr">
+      <c r="BO18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13758,7 +13948,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO19" s="6" t="inlineStr">
+      <c r="BO19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14095,7 +14290,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO20" s="6" t="inlineStr">
+      <c r="BO20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14432,7 +14632,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO21" s="6" t="inlineStr">
+      <c r="BO21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14769,7 +14974,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO22" s="6" t="inlineStr">
+      <c r="BO22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15106,7 +15316,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO23" s="6" t="inlineStr">
+      <c r="BO23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15443,7 +15658,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO24" s="6" t="inlineStr">
+      <c r="BO24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15780,7 +16000,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO25" s="6" t="inlineStr">
+      <c r="BO25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16117,7 +16342,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO26" s="6" t="inlineStr">
+      <c r="BO26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16454,7 +16684,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO27" s="6" t="inlineStr">
+      <c r="BO27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16791,7 +17026,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO28" s="6" t="inlineStr">
+      <c r="BO28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17128,7 +17368,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO29" s="6" t="inlineStr">
+      <c r="BO29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17465,7 +17710,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO30" s="6" t="inlineStr">
+      <c r="BO30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17802,7 +18052,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO31" s="6" t="inlineStr">
+      <c r="BO31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -18139,7 +18394,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO32" s="6" t="inlineStr">
+      <c r="BO32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -18476,7 +18736,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO33" s="6" t="inlineStr">
+      <c r="BO33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -18813,7 +19078,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO34" s="6" t="inlineStr">
+      <c r="BO34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -19150,7 +19420,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO35" s="6" t="inlineStr">
+      <c r="BO35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP35" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -19487,7 +19762,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO36" s="6" t="inlineStr">
+      <c r="BO36" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP36" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -19824,7 +20104,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO37" s="6" t="inlineStr">
+      <c r="BO37" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP37" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20161,7 +20446,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO38" s="6" t="inlineStr">
+      <c r="BO38" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP38" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20498,7 +20788,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO39" s="6" t="inlineStr">
+      <c r="BO39" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP39" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20506,8 +20801,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BO9"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="A1:BP8"/>
+    <mergeCell ref="A9:BP9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
